--- a/回後買上漲圖表_20260616/回後買上漲_嚴格版(1+2+3)_20260616.xlsx
+++ b/回後買上漲圖表_20260616/回後買上漲_嚴格版(1+2+3)_20260616.xlsx
@@ -491,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -561,28 +561,28 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>6180.TWO</t>
+          <t>4721.TWO</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>橘子</t>
+          <t>美琪瑪</t>
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>48.3</v>
+        <v>101</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>44.6</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>3389</v>
+        <v>4601</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>967</v>
+        <v>1619</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
@@ -603,28 +603,28 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>2347.TW</t>
+          <t>4976.TW</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>佳凌</t>
         </is>
       </c>
       <c r="C3" s="9" t="n">
-        <v>93</v>
+        <v>34.6</v>
       </c>
       <c r="D3" s="9" t="n">
-        <v>91.40000000000001</v>
+        <v>34.05</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>7038</v>
+        <v>2908</v>
       </c>
       <c r="G3" s="11" t="n">
-        <v>3799</v>
+        <v>1157</v>
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
@@ -645,28 +645,28 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>5880.TW</t>
+          <t>3093.TWO</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>港建*</t>
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>24.6</v>
+        <v>64.7</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>24.35</v>
+        <v>62.4</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>41277</v>
+        <v>3440</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>21235</v>
+        <v>1563</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
@@ -687,28 +687,28 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>3003.TW</t>
+          <t>6166.TW</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>健和興</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C5" s="9" t="n">
-        <v>67.40000000000001</v>
+        <v>141</v>
       </c>
       <c r="D5" s="9" t="n">
-        <v>65.5</v>
+        <v>134.5</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>4806</v>
+        <v>3624</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>2486</v>
+        <v>2210</v>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
@@ -729,28 +729,28 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2379.TW</t>
+          <t>6788.TWO</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>華景電</t>
         </is>
       </c>
       <c r="C6" s="3" t="n">
-        <v>678</v>
+        <v>449</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>644</v>
+        <v>428</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>4254</v>
+        <v>1965</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>2491</v>
+        <v>1194</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
@@ -763,48 +763,6 @@
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
-        <is>
-          <t>點我查看</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>2867.TW</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>三商壽</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>8.529999999999999</v>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>8.48</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="F7" s="11" t="n">
-        <v>37888</v>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>21685</v>
-      </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t>5&gt;10&gt;20 多頭排列</t>
-        </is>
-      </c>
-      <c r="I7" s="12" t="inlineStr">
-        <is>
-          <t>踩10MA</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>點我查看</t>
         </is>
@@ -817,7 +775,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
